--- a/exports/trend_1d/PFC_full_report.xlsx
+++ b/exports/trend_1d/PFC_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q89"/>
+  <dimension ref="A1:U89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>12.03</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42058</v>
+        <v>42059</v>
       </c>
       <c r="H2" t="n">
-        <v>109.2</v>
+        <v>108.1</v>
       </c>
       <c r="I2" t="n">
         <v>108.1224394233548</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K2" t="n">
-        <v>-6.35</v>
+        <v>-7.29</v>
       </c>
       <c r="L2" t="n">
-        <v>7.38</v>
+        <v>7.93</v>
       </c>
       <c r="M2" t="n">
         <v>0.84</v>
@@ -564,7 +587,19 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.54</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42062</v>
+        <v>42065</v>
       </c>
       <c r="H3" t="n">
-        <v>117.45</v>
+        <v>123.5</v>
       </c>
       <c r="I3" t="n">
         <v>120.2923173834737</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.65</v>
+        <v>-14.25</v>
       </c>
       <c r="L3" t="n">
-        <v>9.16</v>
+        <v>15.08</v>
       </c>
       <c r="M3" t="n">
         <v>0.83</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>12.68</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42075</v>
+        <v>42076</v>
       </c>
       <c r="H4" t="n">
-        <v>115.8</v>
+        <v>108.95</v>
       </c>
       <c r="I4" t="n">
         <v>109.9449880647029</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.23</v>
+        <v>-11.78</v>
       </c>
       <c r="L4" t="n">
-        <v>8.58</v>
+        <v>12.31</v>
       </c>
       <c r="M4" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>4.45</v>
+        <v>5.92</v>
       </c>
       <c r="O4" t="n">
         <v>5.15</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>15.43</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42265</v>
+        <v>42268</v>
       </c>
       <c r="H5" t="n">
-        <v>92.2</v>
+        <v>97.65000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>94.24290046940922</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="K5" t="n">
-        <v>15.37</v>
+        <v>10.37</v>
       </c>
       <c r="L5" t="n">
         <v>7.3</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42089</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>16.37</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42314</v>
+        <v>42317</v>
       </c>
       <c r="H6" t="n">
-        <v>92.84999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="I6" t="n">
         <v>91.24525691912132</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.92</v>
+        <v>-7.63</v>
       </c>
       <c r="L6" t="n">
         <v>9.06</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42271</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>3</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>14.56</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42404</v>
+        <v>42405</v>
       </c>
       <c r="H7" t="n">
-        <v>67.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="I7" t="n">
         <v>70.38105183901602</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K7" t="n">
-        <v>25.28</v>
+        <v>21.51</v>
       </c>
       <c r="L7" t="n">
         <v>3.16</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42334</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>16.37</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42410</v>
+        <v>42411</v>
       </c>
       <c r="H8" t="n">
-        <v>63.2</v>
+        <v>60.15</v>
       </c>
       <c r="I8" t="n">
         <v>62.2268798266557</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K8" t="n">
-        <v>-10.73</v>
+        <v>-15.04</v>
       </c>
       <c r="L8" t="n">
-        <v>12.01</v>
+        <v>16.1</v>
       </c>
       <c r="M8" t="n">
         <v>1.39</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>22.35</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42485</v>
+        <v>42486</v>
       </c>
       <c r="H9" t="n">
-        <v>69.40000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="I9" t="n">
         <v>70.90342148223804</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K9" t="n">
-        <v>-15.38</v>
+        <v>-21.03</v>
       </c>
       <c r="L9" t="n">
-        <v>18.95</v>
+        <v>21.53</v>
       </c>
       <c r="M9" t="n">
         <v>1.92</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42425</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -990,22 +1109,22 @@
         <v>12.63</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42531</v>
+        <v>42534</v>
       </c>
       <c r="H10" t="n">
-        <v>65.45</v>
+        <v>64.05</v>
       </c>
       <c r="I10" t="n">
         <v>65.3018498543277</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K10" t="n">
-        <v>-10.1</v>
+        <v>-12.02</v>
       </c>
       <c r="L10" t="n">
-        <v>10.85</v>
+        <v>12.64</v>
       </c>
       <c r="M10" t="n">
         <v>1.67</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>8.26</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42551</v>
+        <v>42552</v>
       </c>
       <c r="H11" t="n">
-        <v>67.75</v>
+        <v>70.95</v>
       </c>
       <c r="I11" t="n">
         <v>69.20822008789872</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K11" t="n">
-        <v>-5.78</v>
+        <v>-10.77</v>
       </c>
       <c r="L11" t="n">
-        <v>7.18</v>
+        <v>11.24</v>
       </c>
       <c r="M11" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.76</v>
+        <v>4.72</v>
       </c>
       <c r="O11" t="n">
         <v>-2.14</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>9.18</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H12" t="n">
-        <v>95.25</v>
+        <v>91.2</v>
       </c>
       <c r="I12" t="n">
         <v>91.65146839230408</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K12" t="n">
-        <v>34.25</v>
+        <v>28.54</v>
       </c>
       <c r="L12" t="n">
         <v>3.31</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>11.93</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42663</v>
+        <v>42664</v>
       </c>
       <c r="H13" t="n">
-        <v>99.15000000000001</v>
+        <v>102.1</v>
       </c>
       <c r="I13" t="n">
         <v>102.0814502303849</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>-8.720000000000001</v>
+        <v>-11.95</v>
       </c>
       <c r="L13" t="n">
-        <v>11.95</v>
+        <v>12.17</v>
       </c>
       <c r="M13" t="n">
         <v>0.8100000000000001</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>9.94</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42676</v>
+        <v>42677</v>
       </c>
       <c r="H14" t="n">
-        <v>94.55</v>
+        <v>92.5</v>
       </c>
       <c r="I14" t="n">
         <v>94.12426080374814</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.39</v>
+        <v>-9.4</v>
       </c>
       <c r="L14" t="n">
-        <v>7.54</v>
+        <v>9.75</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>10.82</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42691</v>
+        <v>42692</v>
       </c>
       <c r="H15" t="n">
-        <v>96.75</v>
+        <v>100.05</v>
       </c>
       <c r="I15" t="n">
         <v>99.58896833799818</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.59</v>
+        <v>-8.16</v>
       </c>
       <c r="L15" t="n">
-        <v>6.7</v>
+        <v>8.76</v>
       </c>
       <c r="M15" t="n">
         <v>1.87</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>13.36</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42726</v>
+        <v>42727</v>
       </c>
       <c r="H16" t="n">
-        <v>99.8</v>
+        <v>95.75</v>
       </c>
       <c r="I16" t="n">
         <v>97.43815385398342</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.25</v>
+        <v>-4.3</v>
       </c>
       <c r="L16" t="n">
         <v>5.55</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42698</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>13.42</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42740</v>
+        <v>42741</v>
       </c>
       <c r="H17" t="n">
-        <v>102.8</v>
+        <v>103.55</v>
       </c>
       <c r="I17" t="n">
         <v>103.3163229508676</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.36</v>
+        <v>-8.15</v>
       </c>
       <c r="L17" t="n">
-        <v>7.89</v>
+        <v>10.18</v>
       </c>
       <c r="M17" t="n">
         <v>0.82</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>9.67</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42874</v>
+        <v>42877</v>
       </c>
       <c r="H18" t="n">
-        <v>123.65</v>
+        <v>120.4</v>
       </c>
       <c r="I18" t="n">
         <v>121.8903722586904</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="K18" t="n">
-        <v>19.41</v>
+        <v>16.27</v>
       </c>
       <c r="L18" t="n">
         <v>2.32</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>11.57</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>42951</v>
+        <v>42954</v>
       </c>
       <c r="H19" t="n">
-        <v>102.75</v>
+        <v>109.35</v>
       </c>
       <c r="I19" t="n">
         <v>105.1147437243838</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K19" t="n">
-        <v>14.66</v>
+        <v>9.18</v>
       </c>
       <c r="L19" t="n">
         <v>4.24</v>
@@ -1524,7 +1751,7 @@
         <v>1.69</v>
       </c>
       <c r="N19" t="n">
-        <v>3.38</v>
+        <v>6.42</v>
       </c>
       <c r="O19" t="n">
         <v>-2.63</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4</v>
+      </c>
+      <c r="U19" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1560,25 +1799,25 @@
         <v>11.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>42957</v>
+        <v>42958</v>
       </c>
       <c r="H20" t="n">
-        <v>99.65000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="I20" t="n">
         <v>99.1381316424318</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>-8.869999999999999</v>
+        <v>-13.95</v>
       </c>
       <c r="L20" t="n">
-        <v>10.29</v>
+        <v>15.64</v>
       </c>
       <c r="M20" t="n">
-        <v>1.21</v>
+        <v>5.67</v>
       </c>
       <c r="N20" t="n">
         <v>7.13</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>14.44</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>42996</v>
+        <v>42997</v>
       </c>
       <c r="H21" t="n">
-        <v>105</v>
+        <v>107.65</v>
       </c>
       <c r="I21" t="n">
         <v>106.9859521464604</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K21" t="n">
-        <v>-11.58</v>
+        <v>-14.4</v>
       </c>
       <c r="L21" t="n">
-        <v>14.19</v>
+        <v>14.93</v>
       </c>
       <c r="M21" t="n">
         <v>1.29</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.779999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43004</v>
+        <v>43005</v>
       </c>
       <c r="H22" t="n">
-        <v>101.1</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>98.75385970172711</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.08</v>
+        <v>-10.22</v>
       </c>
       <c r="L22" t="n">
-        <v>7.8</v>
+        <v>11.1</v>
       </c>
       <c r="M22" t="n">
         <v>0.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>13.34</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43025</v>
+        <v>43026</v>
       </c>
       <c r="H23" t="n">
-        <v>102.55</v>
+        <v>105.4</v>
       </c>
       <c r="I23" t="n">
         <v>104.6129629273723</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.1</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>6.62</v>
+        <v>9.83</v>
       </c>
       <c r="M23" t="n">
         <v>0.77</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>10.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43048</v>
+        <v>43049</v>
       </c>
       <c r="H24" t="n">
-        <v>110.3</v>
+        <v>101.35</v>
       </c>
       <c r="I24" t="n">
         <v>105.9935919733136</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" t="n">
-        <v>4.65</v>
+        <v>-3.84</v>
       </c>
       <c r="L24" t="n">
-        <v>3.04</v>
+        <v>4.7</v>
       </c>
       <c r="M24" t="n">
-        <v>1.14</v>
+        <v>4.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3.63</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>2.78</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>15.64</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43103</v>
+        <v>43104</v>
       </c>
       <c r="H25" t="n">
-        <v>99</v>
+        <v>100.25</v>
       </c>
       <c r="I25" t="n">
         <v>100.0790244554931</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K25" t="n">
-        <v>2.32</v>
+        <v>1.09</v>
       </c>
       <c r="L25" t="n">
         <v>4.05</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43069</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -1902,25 +2213,25 @@
         <v>7.36</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43124</v>
+        <v>43125</v>
       </c>
       <c r="H26" t="n">
-        <v>97.2</v>
+        <v>95</v>
       </c>
       <c r="I26" t="n">
         <v>95.05376255653071</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.04</v>
+        <v>-5.24</v>
       </c>
       <c r="L26" t="n">
         <v>5.74</v>
       </c>
       <c r="M26" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="N26" t="n">
         <v>2.91</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43251</v>
+        <v>43252</v>
       </c>
       <c r="H27" t="n">
-        <v>64.45</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>64.78003937516614</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K27" t="n">
-        <v>32.16</v>
+        <v>30.63</v>
       </c>
       <c r="L27" t="n">
         <v>2.63</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43153</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>13.21</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43277</v>
+        <v>43278</v>
       </c>
       <c r="H28" t="n">
-        <v>64.45</v>
+        <v>60.5</v>
       </c>
       <c r="I28" t="n">
         <v>60.62409221681228</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.2</v>
+        <v>-8.19</v>
       </c>
       <c r="L28" t="n">
-        <v>6.83</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="M28" t="n">
         <v>0.83</v>
       </c>
       <c r="N28" t="n">
-        <v>3.66</v>
+        <v>6.13</v>
       </c>
       <c r="O28" t="n">
         <v>2.25</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>14.53</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43305</v>
+        <v>43306</v>
       </c>
       <c r="H29" t="n">
-        <v>61.2</v>
+        <v>62.45</v>
       </c>
       <c r="I29" t="n">
         <v>62.43429004848093</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.16</v>
+        <v>-3.22</v>
       </c>
       <c r="L29" t="n">
         <v>6.94</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>14.75</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43370</v>
+        <v>43371</v>
       </c>
       <c r="H30" t="n">
-        <v>63.3</v>
+        <v>60.9</v>
       </c>
       <c r="I30" t="n">
         <v>62.12517394258887</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K30" t="n">
-        <v>1.36</v>
+        <v>-2.48</v>
       </c>
       <c r="L30" t="n">
         <v>6.65</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>19.34</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43399</v>
+        <v>43402</v>
       </c>
       <c r="H31" t="n">
-        <v>67.40000000000001</v>
+        <v>73.34999999999999</v>
       </c>
       <c r="I31" t="n">
         <v>69.68207622638519</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K31" t="n">
-        <v>-10.67</v>
+        <v>-20.44</v>
       </c>
       <c r="L31" t="n">
-        <v>12.89</v>
+        <v>21.35</v>
       </c>
       <c r="M31" t="n">
         <v>1.26</v>
       </c>
       <c r="N31" t="n">
-        <v>4.57</v>
+        <v>8.83</v>
       </c>
       <c r="O31" t="n">
         <v>-3.79</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>19.53</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43433</v>
+        <v>43434</v>
       </c>
       <c r="H32" t="n">
-        <v>73.55</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="I32" t="n">
         <v>73.36811055984407</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K32" t="n">
-        <v>0.27</v>
+        <v>-5.73</v>
       </c>
       <c r="L32" t="n">
         <v>9.130000000000001</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>24.4</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43461</v>
+        <v>43462</v>
       </c>
       <c r="H33" t="n">
-        <v>80.5</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="I33" t="n">
         <v>83.24734965147108</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K33" t="n">
-        <v>-16.41</v>
+        <v>-21.62</v>
       </c>
       <c r="L33" t="n">
-        <v>19.67</v>
+        <v>23.57</v>
       </c>
       <c r="M33" t="n">
         <v>0.89</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43461</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>14.99</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43592</v>
+        <v>43593</v>
       </c>
       <c r="H34" t="n">
-        <v>88.5</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="I34" t="n">
         <v>87.94067941174833</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K34" t="n">
-        <v>5.23</v>
+        <v>2.44</v>
       </c>
       <c r="L34" t="n">
         <v>6.78</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>5</v>
+      </c>
+      <c r="U34" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>10.81</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H35" t="n">
-        <v>87.25</v>
+        <v>93.5</v>
       </c>
       <c r="I35" t="n">
         <v>92.5552668641939</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K35" t="n">
-        <v>-1.28</v>
+        <v>-8.529999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>3.19</v>
+        <v>10.74</v>
       </c>
       <c r="M35" t="n">
-        <v>0.41</v>
+        <v>2.64</v>
       </c>
       <c r="N35" t="n">
-        <v>1.98</v>
+        <v>7.16</v>
       </c>
       <c r="O35" t="n">
         <v>-2.66</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>11.13</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43655</v>
+        <v>43656</v>
       </c>
       <c r="H36" t="n">
-        <v>102.7</v>
+        <v>99.95</v>
       </c>
       <c r="I36" t="n">
         <v>100.2789210241714</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K36" t="n">
-        <v>9.84</v>
+        <v>6.9</v>
       </c>
       <c r="L36" t="n">
         <v>5.88</v>
       </c>
       <c r="M36" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="N36" t="n">
         <v>4.55</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>13.63</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43760</v>
+        <v>43761</v>
       </c>
       <c r="H37" t="n">
-        <v>81.2</v>
+        <v>83.55</v>
       </c>
       <c r="I37" t="n">
         <v>82.99428738830049</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K37" t="n">
-        <v>18.76</v>
+        <v>16.41</v>
       </c>
       <c r="L37" t="n">
         <v>3.8</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>13.46</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43847</v>
+        <v>43850</v>
       </c>
       <c r="H38" t="n">
-        <v>97.55</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="I38" t="n">
         <v>90.44570043924749</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K38" t="n">
-        <v>16.76</v>
+        <v>7.6</v>
       </c>
       <c r="L38" t="n">
         <v>4.73</v>
       </c>
       <c r="M38" t="n">
-        <v>2.41</v>
+        <v>4.1</v>
       </c>
       <c r="N38" t="n">
-        <v>4.95</v>
+        <v>7.84</v>
       </c>
       <c r="O38" t="n">
         <v>2.89</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>4</v>
+      </c>
+      <c r="U38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>12.67</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43865</v>
+        <v>43866</v>
       </c>
       <c r="H39" t="n">
-        <v>92.84999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="I39" t="n">
         <v>97.45614594180972</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.28</v>
+        <v>-9.34</v>
       </c>
       <c r="L39" t="n">
-        <v>7.06</v>
+        <v>10.85</v>
       </c>
       <c r="M39" t="n">
         <v>2.15</v>
       </c>
       <c r="N39" t="n">
-        <v>3.9</v>
+        <v>5.87</v>
       </c>
       <c r="O39" t="n">
         <v>-7.84</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>14.7</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>43888</v>
+        <v>43889</v>
       </c>
       <c r="H40" t="n">
-        <v>100.1</v>
+        <v>87.55</v>
       </c>
       <c r="I40" t="n">
         <v>93.78017102444593</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
-        <v>1.83</v>
+        <v>-10.94</v>
       </c>
       <c r="L40" t="n">
-        <v>4.53</v>
+        <v>11.6</v>
       </c>
       <c r="M40" t="n">
-        <v>0.78</v>
+        <v>10.49</v>
       </c>
       <c r="N40" t="n">
-        <v>2.17</v>
+        <v>12.54</v>
       </c>
       <c r="O40" t="n">
         <v>5.87</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>16.5</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44001</v>
+        <v>44004</v>
       </c>
       <c r="H41" t="n">
-        <v>68.15000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="I41" t="n">
         <v>69.84872467782402</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K41" t="n">
-        <v>22.16</v>
+        <v>17.19</v>
       </c>
       <c r="L41" t="n">
         <v>5.54</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>16.25</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44081</v>
+        <v>44082</v>
       </c>
       <c r="H42" t="n">
-        <v>73.84999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I42" t="n">
         <v>72.24803436056641</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K42" t="n">
-        <v>1.86</v>
+        <v>-0.83</v>
       </c>
       <c r="L42" t="n">
         <v>12.97</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>13.99</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44139</v>
+        <v>44140</v>
       </c>
       <c r="H43" t="n">
-        <v>72.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I43" t="n">
         <v>74.41050401739628</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.39</v>
+        <v>-4.17</v>
       </c>
       <c r="L43" t="n">
         <v>6.75</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H44" t="n">
-        <v>91.40000000000001</v>
+        <v>89.25</v>
       </c>
       <c r="I44" t="n">
         <v>89.33052747248064</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K44" t="n">
-        <v>22.03</v>
+        <v>19.16</v>
       </c>
       <c r="L44" t="n">
         <v>2.67</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>11.25</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44229</v>
+        <v>44230</v>
       </c>
       <c r="H45" t="n">
-        <v>95.15000000000001</v>
+        <v>99.95</v>
       </c>
       <c r="I45" t="n">
         <v>97.3284505290929</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.61</v>
+        <v>-11.99</v>
       </c>
       <c r="L45" t="n">
-        <v>8.460000000000001</v>
+        <v>12.89</v>
       </c>
       <c r="M45" t="n">
         <v>1.25</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>12.98</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44246</v>
+        <v>44249</v>
       </c>
       <c r="H46" t="n">
-        <v>99.45</v>
+        <v>97.3</v>
       </c>
       <c r="I46" t="n">
         <v>97.3136191707149</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.5</v>
+        <v>-2.65</v>
       </c>
       <c r="L46" t="n">
         <v>4.9</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>13.02</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44265</v>
+        <v>44267</v>
       </c>
       <c r="H47" t="n">
-        <v>107.5</v>
+        <v>110.15</v>
       </c>
       <c r="I47" t="n">
         <v>108.7188055158846</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K47" t="n">
-        <v>-10.48</v>
+        <v>-13.21</v>
       </c>
       <c r="L47" t="n">
-        <v>14.03</v>
+        <v>15.52</v>
       </c>
       <c r="M47" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="N47" t="n">
         <v>4.32</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44252</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>11.28</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44273</v>
+        <v>44274</v>
       </c>
       <c r="H48" t="n">
-        <v>105.6</v>
+        <v>98.8</v>
       </c>
       <c r="I48" t="n">
         <v>98.91092749480579</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K48" t="n">
-        <v>-4.13</v>
+        <v>-10.3</v>
       </c>
       <c r="L48" t="n">
-        <v>5.31</v>
+        <v>13.25</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>6.82</v>
       </c>
       <c r="N48" t="n">
-        <v>2.72</v>
+        <v>6.44</v>
       </c>
       <c r="O48" t="n">
         <v>2.47</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S48" t="b">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>13.38</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44336</v>
+        <v>44337</v>
       </c>
       <c r="H49" t="n">
-        <v>93.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="I49" t="n">
         <v>94.32150441889084</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K49" t="n">
-        <v>5.26</v>
+        <v>3.74</v>
       </c>
       <c r="L49" t="n">
         <v>0.91</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>8.27</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44490</v>
+        <v>44491</v>
       </c>
       <c r="H50" t="n">
-        <v>113.6</v>
+        <v>109.7</v>
       </c>
       <c r="I50" t="n">
         <v>110.3235552730462</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="K50" t="n">
-        <v>19.45</v>
+        <v>15.35</v>
       </c>
       <c r="L50" t="n">
         <v>2.21</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>6</v>
+      </c>
+      <c r="U50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>12.75</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H51" t="n">
-        <v>99.05</v>
+        <v>100.7</v>
       </c>
       <c r="I51" t="n">
         <v>100.3552448260461</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K51" t="n">
-        <v>9.710000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L51" t="n">
         <v>4.1</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,25 +4007,25 @@
         <v>6.68</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44582</v>
+        <v>44585</v>
       </c>
       <c r="H52" t="n">
-        <v>96.7</v>
+        <v>93.95</v>
       </c>
       <c r="I52" t="n">
         <v>96.24473297658122</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K52" t="n">
-        <v>-3.97</v>
+        <v>-6.7</v>
       </c>
       <c r="L52" t="n">
-        <v>4.67</v>
+        <v>7.55</v>
       </c>
       <c r="M52" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="N52" t="n">
         <v>3.3</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>8.42</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44641</v>
+        <v>44642</v>
       </c>
       <c r="H53" t="n">
-        <v>92.3</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="I53" t="n">
         <v>93.13887823906394</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K53" t="n">
-        <v>1.76</v>
+        <v>0.85</v>
       </c>
       <c r="L53" t="n">
         <v>5.91</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>3</v>
+      </c>
+      <c r="U53" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>8.890000000000001</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44683</v>
+        <v>44685</v>
       </c>
       <c r="H54" t="n">
-        <v>93.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="I54" t="n">
         <v>91.49173369973455</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K54" t="n">
-        <v>0.38</v>
+        <v>-2.2</v>
       </c>
       <c r="L54" t="n">
         <v>4.13</v>
@@ -3519,7 +4166,7 @@
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>2.52</v>
+        <v>2.57</v>
       </c>
       <c r="O54" t="n">
         <v>0.92</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>8.82</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44743</v>
+        <v>44746</v>
       </c>
       <c r="H55" t="n">
-        <v>84.7</v>
+        <v>86.05</v>
       </c>
       <c r="I55" t="n">
         <v>85.18837708201112</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K55" t="n">
-        <v>7.03</v>
+        <v>5.54</v>
       </c>
       <c r="L55" t="n">
         <v>3.4</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>3</v>
+      </c>
+      <c r="U55" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>7.23</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44806</v>
+        <v>44809</v>
       </c>
       <c r="H56" t="n">
-        <v>92.7</v>
+        <v>91.55</v>
       </c>
       <c r="I56" t="n">
         <v>91.75163593793916</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K56" t="n">
-        <v>7.73</v>
+        <v>6.39</v>
       </c>
       <c r="L56" t="n">
         <v>1.74</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>3</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>6.91</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44859</v>
+        <v>44861</v>
       </c>
       <c r="H57" t="n">
-        <v>84.95</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>85.81210885291357</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="K57" t="n">
-        <v>7.21</v>
+        <v>3.99</v>
       </c>
       <c r="L57" t="n">
         <v>3.93</v>
@@ -3690,7 +4373,7 @@
         <v>1.85</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="O57" t="n">
         <v>-1.24</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.3</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H58" t="n">
-        <v>109.8</v>
+        <v>105.45</v>
       </c>
       <c r="I58" t="n">
         <v>108.2877957612275</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K58" t="n">
-        <v>24.91</v>
+        <v>19.97</v>
       </c>
       <c r="L58" t="n">
         <v>3.64</v>
@@ -3747,7 +4442,7 @@
         <v>2.1</v>
       </c>
       <c r="N58" t="n">
-        <v>2.87</v>
+        <v>3.96</v>
       </c>
       <c r="O58" t="n">
         <v>3.47</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>11.36</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>44925</v>
+        <v>44928</v>
       </c>
       <c r="H59" t="n">
-        <v>112.9</v>
+        <v>119.75</v>
       </c>
       <c r="I59" t="n">
         <v>117.4331622895717</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.06</v>
+        <v>-13.56</v>
       </c>
       <c r="L59" t="n">
-        <v>8.630000000000001</v>
+        <v>14.22</v>
       </c>
       <c r="M59" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="N59" t="n">
-        <v>3.41</v>
+        <v>6.07</v>
       </c>
       <c r="O59" t="n">
         <v>-3.96</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.92</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>44950</v>
+        <v>44951</v>
       </c>
       <c r="H60" t="n">
-        <v>119.5</v>
+        <v>114.75</v>
       </c>
       <c r="I60" t="n">
         <v>115.4202217004658</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.21</v>
+        <v>-4.18</v>
       </c>
       <c r="L60" t="n">
         <v>5.72</v>
@@ -3861,7 +4580,7 @@
         <v>0.32</v>
       </c>
       <c r="N60" t="n">
-        <v>2.63</v>
+        <v>3.97</v>
       </c>
       <c r="O60" t="n">
         <v>6.07</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>10.8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>44987</v>
+        <v>44988</v>
       </c>
       <c r="H61" t="n">
-        <v>120.3</v>
+        <v>124.1</v>
       </c>
       <c r="I61" t="n">
         <v>121.7623336387338</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.84</v>
+        <v>-8.15</v>
       </c>
       <c r="L61" t="n">
-        <v>5.88</v>
+        <v>8.41</v>
       </c>
       <c r="M61" t="n">
         <v>1.06</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>10.17</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45002</v>
+        <v>45005</v>
       </c>
       <c r="H62" t="n">
-        <v>124.7</v>
+        <v>120.7</v>
       </c>
       <c r="I62" t="n">
         <v>122.6671630576172</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K62" t="n">
-        <v>0.48</v>
+        <v>-2.74</v>
       </c>
       <c r="L62" t="n">
-        <v>2.86</v>
+        <v>3.55</v>
       </c>
       <c r="M62" t="n">
-        <v>0.67</v>
+        <v>1.12</v>
       </c>
       <c r="N62" t="n">
-        <v>2.17</v>
+        <v>3.21</v>
       </c>
       <c r="O62" t="n">
         <v>3.16</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>11.43</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H63" t="n">
-        <v>125.9</v>
+        <v>133.1</v>
       </c>
       <c r="I63" t="n">
         <v>129.6077700018996</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.31</v>
+        <v>-10.27</v>
       </c>
       <c r="L63" t="n">
-        <v>4.81</v>
+        <v>10.6</v>
       </c>
       <c r="M63" t="n">
         <v>0.75</v>
       </c>
       <c r="N63" t="n">
-        <v>3.03</v>
+        <v>5.72</v>
       </c>
       <c r="O63" t="n">
         <v>-3.21</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>12.06</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="H64" t="n">
-        <v>426.1</v>
+        <v>412.4</v>
       </c>
       <c r="I64" t="n">
         <v>420.3291243287526</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K64" t="n">
-        <v>220.14</v>
+        <v>209.84</v>
       </c>
       <c r="L64" t="n">
         <v>6.35</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>217</v>
+        <v>218</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>11</v>
+      </c>
+      <c r="U64" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>14.76</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45384</v>
+        <v>45385</v>
       </c>
       <c r="H65" t="n">
-        <v>407.55</v>
+        <v>417.25</v>
       </c>
       <c r="I65" t="n">
         <v>410.2988274676405</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K65" t="n">
-        <v>1.18</v>
+        <v>-1.18</v>
       </c>
       <c r="L65" t="n">
         <v>5.49</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>13.09</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45418</v>
+        <v>45419</v>
       </c>
       <c r="H66" t="n">
-        <v>437.8</v>
+        <v>421.55</v>
       </c>
       <c r="I66" t="n">
         <v>429.1963266480936</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K66" t="n">
-        <v>4.93</v>
+        <v>1.03</v>
       </c>
       <c r="L66" t="n">
         <v>7.73</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>16.64</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45435</v>
+        <v>45436</v>
       </c>
       <c r="H67" t="n">
-        <v>467.25</v>
+        <v>491.65</v>
       </c>
       <c r="I67" t="n">
         <v>475.4578190948105</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K67" t="n">
-        <v>-10.84</v>
+        <v>-16.63</v>
       </c>
       <c r="L67" t="n">
-        <v>12.68</v>
+        <v>18.47</v>
       </c>
       <c r="M67" t="n">
         <v>1.48</v>
       </c>
       <c r="N67" t="n">
-        <v>4.59</v>
+        <v>5.22</v>
       </c>
       <c r="O67" t="n">
         <v>-3.71</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>13.23</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45446</v>
+        <v>45447</v>
       </c>
       <c r="H68" t="n">
-        <v>554.8</v>
+        <v>426.75</v>
       </c>
       <c r="I68" t="n">
         <v>463.629031173102</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K68" t="n">
-        <v>12.84</v>
+        <v>-13.2</v>
       </c>
       <c r="L68" t="n">
-        <v>5.34</v>
+        <v>15.37</v>
       </c>
       <c r="M68" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.78</v>
       </c>
       <c r="N68" t="n">
-        <v>1.89</v>
+        <v>23.08</v>
       </c>
       <c r="O68" t="n">
         <v>5.22</v>
@@ -4326,7 +5141,19 @@
         <v>1</v>
       </c>
       <c r="Q68" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>38.35</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45478</v>
+        <v>45481</v>
       </c>
       <c r="H69" t="n">
-        <v>534.25</v>
+        <v>549.75</v>
       </c>
       <c r="I69" t="n">
         <v>538.6244847497874</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K69" t="n">
-        <v>-25.19</v>
+        <v>-28.82</v>
       </c>
       <c r="L69" t="n">
-        <v>27.69</v>
+        <v>31.17</v>
       </c>
       <c r="M69" t="n">
         <v>4.21</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>10.4</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45506</v>
+        <v>45509</v>
       </c>
       <c r="H70" t="n">
-        <v>526.3</v>
+        <v>498.05</v>
       </c>
       <c r="I70" t="n">
         <v>509.7092729579309</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.27</v>
+        <v>-9.4</v>
       </c>
       <c r="L70" t="n">
-        <v>8.140000000000001</v>
+        <v>10.74</v>
       </c>
       <c r="M70" t="n">
-        <v>1.45</v>
+        <v>4.03</v>
       </c>
       <c r="N70" t="n">
-        <v>3.87</v>
+        <v>5.37</v>
       </c>
       <c r="O70" t="n">
         <v>2.9</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,22 +5318,22 @@
         <v>14.13</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45532</v>
+        <v>45533</v>
       </c>
       <c r="H71" t="n">
-        <v>539.25</v>
+        <v>554.45</v>
       </c>
       <c r="I71" t="n">
         <v>544.0900622024591</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K71" t="n">
-        <v>-8.27</v>
+        <v>-11.32</v>
       </c>
       <c r="L71" t="n">
-        <v>9.529999999999999</v>
+        <v>11.74</v>
       </c>
       <c r="M71" t="n">
         <v>4.31</v>
@@ -4497,7 +5348,19 @@
         <v>1</v>
       </c>
       <c r="Q71" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S71" t="b">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>1</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>10.02</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45544</v>
+        <v>45545</v>
       </c>
       <c r="H72" t="n">
-        <v>523.6</v>
+        <v>510.75</v>
       </c>
       <c r="I72" t="n">
         <v>513.96376859493</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K72" t="n">
-        <v>-5.56</v>
+        <v>-7.88</v>
       </c>
       <c r="L72" t="n">
-        <v>7.44</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M72" t="n">
         <v>1.85</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>11.91</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45622</v>
+        <v>45623</v>
       </c>
       <c r="H73" t="n">
-        <v>484.4</v>
+        <v>491.1</v>
       </c>
       <c r="I73" t="n">
         <v>485.3140035378854</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K73" t="n">
-        <v>5.16</v>
+        <v>3.85</v>
       </c>
       <c r="L73" t="n">
         <v>3.48</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>12.64</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H74" t="n">
-        <v>480.45</v>
+        <v>453.3</v>
       </c>
       <c r="I74" t="n">
         <v>475.8214098963492</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.17</v>
+        <v>-7.7</v>
       </c>
       <c r="L74" t="n">
-        <v>4.35</v>
+        <v>8.17</v>
       </c>
       <c r="M74" t="n">
         <v>1.48</v>
       </c>
       <c r="N74" t="n">
-        <v>2.27</v>
+        <v>5.65</v>
       </c>
       <c r="O74" t="n">
         <v>1.38</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>13.27</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>45737</v>
+        <v>45740</v>
       </c>
       <c r="H75" t="n">
-        <v>407.8</v>
+        <v>425.5</v>
       </c>
       <c r="I75" t="n">
         <v>414.6272635373242</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K75" t="n">
-        <v>10.04</v>
+        <v>6.13</v>
       </c>
       <c r="L75" t="n">
         <v>6.44</v>
@@ -4725,7 +5624,19 @@
         <v>1</v>
       </c>
       <c r="Q75" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>4</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>11.21</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>45784</v>
+        <v>45785</v>
       </c>
       <c r="H76" t="n">
-        <v>404.3</v>
+        <v>390.3</v>
       </c>
       <c r="I76" t="n">
         <v>390.9005424204937</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K76" t="n">
-        <v>-4.98</v>
+        <v>-8.27</v>
       </c>
       <c r="L76" t="n">
         <v>12.6</v>
@@ -4782,7 +5693,19 @@
         <v>1</v>
       </c>
       <c r="Q76" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>13.8</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>45814</v>
+        <v>45817</v>
       </c>
       <c r="H77" t="n">
-        <v>418.4</v>
+        <v>431</v>
       </c>
       <c r="I77" t="n">
         <v>430.8024935910393</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K77" t="n">
-        <v>-7.2</v>
+        <v>-10.43</v>
       </c>
       <c r="L77" t="n">
-        <v>8.76</v>
+        <v>10.84</v>
       </c>
       <c r="M77" t="n">
         <v>3.91</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,22 +5801,22 @@
         <v>8.84</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>45825</v>
+        <v>45826</v>
       </c>
       <c r="H78" t="n">
-        <v>403.1</v>
+        <v>397.05</v>
       </c>
       <c r="I78" t="n">
         <v>398.436492142321</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.47</v>
+        <v>-7.88</v>
       </c>
       <c r="L78" t="n">
-        <v>7.84</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="M78" t="n">
         <v>3.55</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,22 +5870,22 @@
         <v>9.41</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>45847</v>
+        <v>45848</v>
       </c>
       <c r="H79" t="n">
-        <v>417.75</v>
+        <v>429.45</v>
       </c>
       <c r="I79" t="n">
         <v>427.6635578489535</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K79" t="n">
-        <v>-5.21</v>
+        <v>-8.16</v>
       </c>
       <c r="L79" t="n">
-        <v>8.27</v>
+        <v>8.92</v>
       </c>
       <c r="M79" t="n">
         <v>2.09</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>2</v>
+      </c>
+      <c r="U79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>7.34</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>45889</v>
+        <v>45890</v>
       </c>
       <c r="H80" t="n">
-        <v>403.4</v>
+        <v>400.25</v>
       </c>
       <c r="I80" t="n">
         <v>403.3396696517944</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K80" t="n">
-        <v>-6.07</v>
+        <v>-6.8</v>
       </c>
       <c r="L80" t="n">
-        <v>6.54</v>
+        <v>7.02</v>
       </c>
       <c r="M80" t="n">
         <v>1.29</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>2</v>
+      </c>
+      <c r="U80" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="81">
@@ -5037,22 +6008,22 @@
         <v>7.59</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="H81" t="n">
-        <v>404.8</v>
+        <v>408</v>
       </c>
       <c r="I81" t="n">
         <v>405.4460557609099</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K81" t="n">
-        <v>-1.14</v>
+        <v>-1.94</v>
       </c>
       <c r="L81" t="n">
-        <v>1.97</v>
+        <v>2.85</v>
       </c>
       <c r="M81" t="n">
         <v>0.68</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>2</v>
+      </c>
+      <c r="U81" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="82">
@@ -5094,22 +6077,22 @@
         <v>4.78</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="H82" t="n">
-        <v>396.6</v>
+        <v>393.6</v>
       </c>
       <c r="I82" t="n">
         <v>393.8388801918945</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K82" t="n">
-        <v>-2.79</v>
+        <v>-3.53</v>
       </c>
       <c r="L82" t="n">
-        <v>3.55</v>
+        <v>3.87</v>
       </c>
       <c r="M82" t="n">
         <v>0.46</v>
@@ -5124,7 +6107,19 @@
         <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R82" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S82" t="b">
+        <v>1</v>
+      </c>
+      <c r="T82" t="n">
+        <v>2</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -5151,19 +6146,19 @@
         <v>5.69</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="H83" t="n">
-        <v>343.4</v>
+        <v>354.9</v>
       </c>
       <c r="I83" t="n">
         <v>353.5378536195611</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K83" t="n">
-        <v>12.75</v>
+        <v>9.83</v>
       </c>
       <c r="L83" t="n">
         <v>4.45</v>
@@ -5181,7 +6176,19 @@
         <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R83" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S83" t="b">
+        <v>1</v>
+      </c>
+      <c r="T83" t="n">
+        <v>3</v>
+      </c>
+      <c r="U83" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="84">
@@ -5208,19 +6215,19 @@
         <v>7.52</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="H84" t="n">
-        <v>396</v>
+        <v>379.5</v>
       </c>
       <c r="I84" t="n">
         <v>387.0661935204548</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="K84" t="n">
-        <v>11.58</v>
+        <v>6.93</v>
       </c>
       <c r="L84" t="n">
         <v>3.51</v>
@@ -5238,7 +6245,19 @@
         <v>0</v>
       </c>
       <c r="Q84" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R84" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S84" t="b">
+        <v>1</v>
+      </c>
+      <c r="T84" t="n">
+        <v>4</v>
+      </c>
+      <c r="U84" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="85">
@@ -5265,22 +6284,22 @@
         <v>13.71</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="H85" t="n">
-        <v>428.05</v>
+        <v>434.9</v>
       </c>
       <c r="I85" t="n">
         <v>431.5116981682448</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>-12.79</v>
+        <v>-14.6</v>
       </c>
       <c r="L85" t="n">
-        <v>14.04</v>
+        <v>15.63</v>
       </c>
       <c r="M85" t="n">
         <v>3.83</v>
@@ -5295,7 +6314,19 @@
         <v>1</v>
       </c>
       <c r="Q85" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R85" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S85" t="b">
+        <v>0</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1</v>
+      </c>
+      <c r="U85" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -5322,19 +6353,19 @@
         <v>11.76</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="H86" t="n">
-        <v>445.75</v>
+        <v>429.8</v>
       </c>
       <c r="I86" t="n">
         <v>438.5572222599208</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K86" t="n">
-        <v>2.49</v>
+        <v>-1.17</v>
       </c>
       <c r="L86" t="n">
         <v>3.41</v>
@@ -5343,7 +6374,7 @@
         <v>2.95</v>
       </c>
       <c r="N86" t="n">
-        <v>3.52</v>
+        <v>3.58</v>
       </c>
       <c r="O86" t="n">
         <v>1.6</v>
@@ -5352,7 +6383,19 @@
         <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R86" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S86" t="b">
+        <v>1</v>
+      </c>
+      <c r="T86" t="n">
+        <v>2</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -5379,19 +6422,19 @@
         <v>11.16</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H87" t="n">
-        <v>342.05</v>
+        <v>344.5</v>
       </c>
       <c r="I87" t="n">
         <v>342.8063114651978</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K87" t="n">
-        <v>20.42</v>
+        <v>19.85</v>
       </c>
       <c r="L87" t="n">
         <v>3.49</v>
@@ -5409,7 +6452,19 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R87" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S87" t="b">
+        <v>1</v>
+      </c>
+      <c r="T87" t="n">
+        <v>6</v>
+      </c>
+      <c r="U87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -5436,28 +6491,28 @@
         <v>7.15</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H88" t="n">
-        <v>326.9</v>
+        <v>316</v>
       </c>
       <c r="I88" t="n">
         <v>320.8632097447417</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K88" t="n">
-        <v>-5.11</v>
+        <v>-8.27</v>
       </c>
       <c r="L88" t="n">
-        <v>7.1</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M88" t="n">
         <v>0.97</v>
       </c>
       <c r="N88" t="n">
-        <v>2.64</v>
+        <v>3.33</v>
       </c>
       <c r="O88" t="n">
         <v>0.72</v>
@@ -5466,7 +6521,19 @@
         <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R88" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S88" t="b">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>1</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -5517,6 +6584,14 @@
       <c r="Q89" t="n">
         <v>4</v>
       </c>
+      <c r="R89" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S89" t="b">
+        <v>1</v>
+      </c>
+      <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10475,7 +11550,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.8</v>
+        <v>49.4</v>
       </c>
     </row>
     <row r="6">
@@ -10485,7 +11560,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -10495,7 +11570,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="8">
@@ -10505,7 +11580,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -10515,7 +11590,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -10525,7 +11600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="11">
@@ -10535,7 +11610,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
@@ -10545,7 +11620,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13">
@@ -10555,7 +11630,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47.1</v>
+        <v>44.8</v>
       </c>
     </row>
     <row r="14">
@@ -10565,7 +11640,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.62</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="15">
@@ -10575,7 +11650,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7.05</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="16">
@@ -10585,7 +11660,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.11</v>
+        <v>-3.42</v>
       </c>
     </row>
     <row r="17">
@@ -10595,7 +11670,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>220.14</v>
+        <v>209.84</v>
       </c>
     </row>
     <row r="18">
@@ -10605,7 +11680,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.7</v>
+        <v>32.2</v>
       </c>
     </row>
     <row r="19">
@@ -10615,7 +11690,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="20">
@@ -10625,7 +11700,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.44</v>
+        <v>7.73</v>
       </c>
     </row>
     <row r="21">
@@ -10635,7 +11710,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.69</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="22">
@@ -10645,7 +11720,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
@@ -10655,7 +11730,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24">
@@ -10665,7 +11740,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.75</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="25">
@@ -10675,7 +11750,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.07</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="26">
@@ -10685,7 +11760,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.79</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="27">
@@ -10695,7 +11770,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.35</v>
+        <v>23.08</v>
       </c>
     </row>
     <row r="28">
@@ -10705,7 +11780,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29">
